--- a/artfynd/A 43829-2025 artfynd.xlsx
+++ b/artfynd/A 43829-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -867,6 +867,694 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128992938</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79156</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>185</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kistmyran, Kistmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>488645</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6837704</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128993014</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79156</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>185</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kistmyran, Kistmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>488649</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6837712</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128992711</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79124</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kistmyran, Kistmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>488662</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6837679</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128993024</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79124</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kistmyran, Kistmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>488655</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6837719</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128992848</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98636</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kistmyran, Kistmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>488645</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6837693</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128994757</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97513</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kistmyran, Kistmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>488752</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6837425</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128993086</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79156</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>185</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kistmyran, Kistmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>488602</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6837816</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43829-2025 artfynd.xlsx
+++ b/artfynd/A 43829-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>128992938</v>
       </c>
       <c r="B4" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128993014</v>
       </c>
       <c r="B5" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128992711</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128993024</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128992848</v>
       </c>
       <c r="B8" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128994757</v>
       </c>
       <c r="B9" t="n">
-        <v>97513</v>
+        <v>97520</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>128993086</v>
       </c>
       <c r="B10" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 43829-2025 artfynd.xlsx
+++ b/artfynd/A 43829-2025 artfynd.xlsx
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128993024</v>
+        <v>128992848</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>98651</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488655</v>
+        <v>488645</v>
       </c>
       <c r="R7" t="n">
-        <v>6837719</v>
+        <v>6837693</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,44 +1245,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128992848</v>
+        <v>128993024</v>
       </c>
       <c r="B8" t="n">
-        <v>98651</v>
+        <v>79034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488645</v>
+        <v>488655</v>
       </c>
       <c r="R8" t="n">
-        <v>6837693</v>
+        <v>6837719</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 43829-2025 artfynd.xlsx
+++ b/artfynd/A 43829-2025 artfynd.xlsx
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128992848</v>
+        <v>128993024</v>
       </c>
       <c r="B7" t="n">
-        <v>98651</v>
+        <v>79034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488645</v>
+        <v>488655</v>
       </c>
       <c r="R7" t="n">
-        <v>6837693</v>
+        <v>6837719</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,44 +1245,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128993024</v>
+        <v>128992848</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>98656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488655</v>
+        <v>488645</v>
       </c>
       <c r="R8" t="n">
-        <v>6837719</v>
+        <v>6837693</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1357,7 +1357,7 @@
         <v>128994757</v>
       </c>
       <c r="B9" t="n">
-        <v>97528</v>
+        <v>97533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 43829-2025 artfynd.xlsx
+++ b/artfynd/A 43829-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>128992938</v>
       </c>
       <c r="B4" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128993014</v>
       </c>
       <c r="B5" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128992711</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128993024</v>
+        <v>128992848</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>98659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488655</v>
+        <v>488645</v>
       </c>
       <c r="R7" t="n">
-        <v>6837719</v>
+        <v>6837693</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,44 +1245,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128992848</v>
+        <v>128993024</v>
       </c>
       <c r="B8" t="n">
-        <v>98656</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488645</v>
+        <v>488655</v>
       </c>
       <c r="R8" t="n">
-        <v>6837693</v>
+        <v>6837719</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1357,7 +1357,7 @@
         <v>128994757</v>
       </c>
       <c r="B9" t="n">
-        <v>97533</v>
+        <v>97536</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>128993086</v>
       </c>
       <c r="B10" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 43829-2025 artfynd.xlsx
+++ b/artfynd/A 43829-2025 artfynd.xlsx
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128992848</v>
+        <v>128993024</v>
       </c>
       <c r="B7" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488645</v>
+        <v>488655</v>
       </c>
       <c r="R7" t="n">
-        <v>6837693</v>
+        <v>6837719</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,44 +1245,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128993024</v>
+        <v>128992848</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488655</v>
+        <v>488645</v>
       </c>
       <c r="R8" t="n">
-        <v>6837719</v>
+        <v>6837693</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 43829-2025 artfynd.xlsx
+++ b/artfynd/A 43829-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>128992938</v>
       </c>
       <c r="B4" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128993014</v>
       </c>
       <c r="B5" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128992711</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128993024</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128992848</v>
       </c>
       <c r="B8" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128994757</v>
       </c>
       <c r="B9" t="n">
-        <v>97536</v>
+        <v>97546</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>128993086</v>
       </c>
       <c r="B10" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 43829-2025 artfynd.xlsx
+++ b/artfynd/A 43829-2025 artfynd.xlsx
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128993024</v>
+        <v>128992848</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>98669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488655</v>
+        <v>488645</v>
       </c>
       <c r="R7" t="n">
-        <v>6837719</v>
+        <v>6837693</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,44 +1245,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128992848</v>
+        <v>128993024</v>
       </c>
       <c r="B8" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488645</v>
+        <v>488655</v>
       </c>
       <c r="R8" t="n">
-        <v>6837693</v>
+        <v>6837719</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 43829-2025 artfynd.xlsx
+++ b/artfynd/A 43829-2025 artfynd.xlsx
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128992848</v>
+        <v>128993024</v>
       </c>
       <c r="B7" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488645</v>
+        <v>488655</v>
       </c>
       <c r="R7" t="n">
-        <v>6837693</v>
+        <v>6837719</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,44 +1245,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128993024</v>
+        <v>128992848</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>98676</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488655</v>
+        <v>488645</v>
       </c>
       <c r="R8" t="n">
-        <v>6837719</v>
+        <v>6837693</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1357,7 +1357,7 @@
         <v>128994757</v>
       </c>
       <c r="B9" t="n">
-        <v>97546</v>
+        <v>97553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 43829-2025 artfynd.xlsx
+++ b/artfynd/A 43829-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>128992938</v>
       </c>
       <c r="B4" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128993014</v>
       </c>
       <c r="B5" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128992711</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128993024</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128992848</v>
       </c>
       <c r="B8" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128994757</v>
       </c>
       <c r="B9" t="n">
-        <v>97553</v>
+        <v>97555</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>128993086</v>
       </c>
       <c r="B10" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 43829-2025 artfynd.xlsx
+++ b/artfynd/A 43829-2025 artfynd.xlsx
@@ -1260,7 +1260,7 @@
         <v>128992848</v>
       </c>
       <c r="B8" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128994757</v>
       </c>
       <c r="B9" t="n">
-        <v>97555</v>
+        <v>97581</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 43829-2025 artfynd.xlsx
+++ b/artfynd/A 43829-2025 artfynd.xlsx
@@ -1260,7 +1260,7 @@
         <v>128992848</v>
       </c>
       <c r="B8" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128994757</v>
       </c>
       <c r="B9" t="n">
-        <v>97581</v>
+        <v>97582</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 43829-2025 artfynd.xlsx
+++ b/artfynd/A 43829-2025 artfynd.xlsx
@@ -1260,7 +1260,7 @@
         <v>128992848</v>
       </c>
       <c r="B8" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128994757</v>
       </c>
       <c r="B9" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 43829-2025 artfynd.xlsx
+++ b/artfynd/A 43829-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>128992938</v>
       </c>
       <c r="B4" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128993014</v>
       </c>
       <c r="B5" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128992711</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128993024</v>
+        <v>128992848</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488655</v>
+        <v>488645</v>
       </c>
       <c r="R7" t="n">
-        <v>6837719</v>
+        <v>6837693</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,44 +1245,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128992848</v>
+        <v>128993024</v>
       </c>
       <c r="B8" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488645</v>
+        <v>488655</v>
       </c>
       <c r="R8" t="n">
-        <v>6837693</v>
+        <v>6837719</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1357,7 +1357,7 @@
         <v>128994757</v>
       </c>
       <c r="B9" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>128993086</v>
       </c>
       <c r="B10" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 43829-2025 artfynd.xlsx
+++ b/artfynd/A 43829-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>128992938</v>
       </c>
       <c r="B4" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128993014</v>
       </c>
       <c r="B5" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128992711</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128992848</v>
       </c>
       <c r="B7" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128993024</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128994757</v>
       </c>
       <c r="B9" t="n">
-        <v>97587</v>
+        <v>97589</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>128993086</v>
       </c>
       <c r="B10" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 43829-2025 artfynd.xlsx
+++ b/artfynd/A 43829-2025 artfynd.xlsx
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128992848</v>
+        <v>128993024</v>
       </c>
       <c r="B7" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488645</v>
+        <v>488655</v>
       </c>
       <c r="R7" t="n">
-        <v>6837693</v>
+        <v>6837719</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,44 +1245,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128993024</v>
+        <v>128992848</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488655</v>
+        <v>488645</v>
       </c>
       <c r="R8" t="n">
-        <v>6837719</v>
+        <v>6837693</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1357,7 +1357,7 @@
         <v>128994757</v>
       </c>
       <c r="B9" t="n">
-        <v>97589</v>
+        <v>97593</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 43829-2025 artfynd.xlsx
+++ b/artfynd/A 43829-2025 artfynd.xlsx
@@ -1260,7 +1260,7 @@
         <v>128992848</v>
       </c>
       <c r="B8" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128994757</v>
       </c>
       <c r="B9" t="n">
-        <v>97593</v>
+        <v>97601</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 43829-2025 artfynd.xlsx
+++ b/artfynd/A 43829-2025 artfynd.xlsx
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128993024</v>
+        <v>128992848</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488655</v>
+        <v>488645</v>
       </c>
       <c r="R7" t="n">
-        <v>6837719</v>
+        <v>6837693</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,44 +1245,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128992848</v>
+        <v>128993024</v>
       </c>
       <c r="B8" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488645</v>
+        <v>488655</v>
       </c>
       <c r="R8" t="n">
-        <v>6837693</v>
+        <v>6837719</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 43829-2025 artfynd.xlsx
+++ b/artfynd/A 43829-2025 artfynd.xlsx
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128992848</v>
+        <v>128993024</v>
       </c>
       <c r="B7" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488645</v>
+        <v>488655</v>
       </c>
       <c r="R7" t="n">
-        <v>6837693</v>
+        <v>6837719</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,44 +1245,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128993024</v>
+        <v>128992848</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488655</v>
+        <v>488645</v>
       </c>
       <c r="R8" t="n">
-        <v>6837719</v>
+        <v>6837693</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 43829-2025 artfynd.xlsx
+++ b/artfynd/A 43829-2025 artfynd.xlsx
@@ -1260,7 +1260,7 @@
         <v>128992848</v>
       </c>
       <c r="B8" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128994757</v>
       </c>
       <c r="B9" t="n">
-        <v>97601</v>
+        <v>97604</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 43829-2025 artfynd.xlsx
+++ b/artfynd/A 43829-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126232063</v>
+        <v>128992938</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488623</v>
+        <v>488645</v>
       </c>
       <c r="R2" t="n">
-        <v>6837734</v>
+        <v>6837704</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126231793</v>
+        <v>128993014</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488826</v>
+        <v>488649</v>
       </c>
       <c r="R3" t="n">
-        <v>6837510</v>
+        <v>6837712</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128992938</v>
+        <v>128993086</v>
       </c>
       <c r="B4" t="n">
-        <v>79076</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488645</v>
+        <v>488602</v>
       </c>
       <c r="R4" t="n">
-        <v>6837704</v>
+        <v>6837816</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,44 +954,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128993014</v>
+        <v>126231793</v>
       </c>
       <c r="B5" t="n">
-        <v>79076</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488649</v>
+        <v>488826</v>
       </c>
       <c r="R5" t="n">
-        <v>6837712</v>
+        <v>6837510</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1051,26 +1051,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128992711</v>
+        <v>126232063</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1098,13 +1098,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488662</v>
+        <v>488623</v>
       </c>
       <c r="R6" t="n">
-        <v>6837679</v>
+        <v>6837734</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1160,14 +1160,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128993024</v>
+        <v>128992711</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488655</v>
+        <v>488662</v>
       </c>
       <c r="R7" t="n">
-        <v>6837719</v>
+        <v>6837679</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,22 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128992848</v>
+        <v>128993024</v>
       </c>
       <c r="B8" t="n">
-        <v>98727</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488645</v>
+        <v>488655</v>
       </c>
       <c r="R8" t="n">
-        <v>6837693</v>
+        <v>6837719</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,66 +1342,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128994757</v>
+        <v>128993607</v>
       </c>
       <c r="B9" t="n">
-        <v>97604</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kistmyran, Kistmyran, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488752</v>
+        <v>488384</v>
       </c>
       <c r="R9" t="n">
-        <v>6837425</v>
+        <v>6837771</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1448,44 +1439,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128993086</v>
+        <v>128994464</v>
       </c>
       <c r="B10" t="n">
-        <v>79076</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,13 +1486,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488602</v>
+        <v>488534</v>
       </c>
       <c r="R10" t="n">
-        <v>6837816</v>
+        <v>6837626</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1554,6 +1545,306 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128992848</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kistmyran, Kistmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>488645</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6837693</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128994757</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kistmyran, Kistmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>488752</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6837425</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126233916</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kistmyran, Kistmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>488558</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6837435</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43829-2025 artfynd.xlsx
+++ b/artfynd/A 43829-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128992938</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128993014</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128993086</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126231793</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126232063</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128992711</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128993024</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128993607</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128994464</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128992848</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1748,6 +1803,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128994757</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1845,8 +1905,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126233916</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>